--- a/Metiers/Reference_lists/RDB_ISSG_Metier_level_7_list.xlsx
+++ b/Metiers/Reference_lists/RDB_ISSG_Metier_level_7_list.xlsx
@@ -1,35 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\dfad\users\joeg\home\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sebastien\Dossiers_courant\_WK_METIER_20180122\2026\MJS_SPAIN_METIERS_TRAPLINES_20261013\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB27A5D-90DB-4049-B066-640403B66DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917109E3-6505-4E16-A93C-5D2C3166AA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-915" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF level7 metier ref list" sheetId="1" r:id="rId1"/>
     <sheet name="School type - FADs codification" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCF level7 metier ref list'!$A$1:$F$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCF level7 metier ref list'!$A$1:$F$95</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="124">
   <si>
     <t>Metier_level7</t>
   </si>
@@ -395,6 +398,12 @@
   </si>
   <si>
     <t>Fishing mode (School type/FADs) codification</t>
+  </si>
+  <si>
+    <t>LLD_LPF_0_6_TPL_SWO</t>
+  </si>
+  <si>
+    <t>LLD_LPF_0_6_TPL</t>
   </si>
 </sst>
 </file>
@@ -935,17 +944,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F93"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="163.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="163.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -965,7 +974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -985,7 +994,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -1005,7 +1014,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
@@ -1025,7 +1034,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -1045,7 +1054,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>31</v>
       </c>
@@ -1065,7 +1074,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
@@ -1085,7 +1094,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
@@ -1105,7 +1114,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>31</v>
       </c>
@@ -1125,7 +1134,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
@@ -1145,7 +1154,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
@@ -1185,7 +1194,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
@@ -1205,7 +1214,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
@@ -1225,7 +1234,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>31</v>
       </c>
@@ -1245,7 +1254,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -1265,7 +1274,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>34</v>
       </c>
@@ -1285,7 +1294,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>31</v>
       </c>
@@ -1305,7 +1314,7 @@
         <v>20230328</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -1325,7 +1334,7 @@
         <v>20230328</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>34</v>
       </c>
@@ -1345,7 +1354,7 @@
         <v>20230328</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>31</v>
       </c>
@@ -1365,7 +1374,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>31</v>
       </c>
@@ -1385,7 +1394,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -1405,7 +1414,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>34</v>
       </c>
@@ -1425,7 +1434,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>35</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>31</v>
       </c>
@@ -1465,7 +1474,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
@@ -1485,7 +1494,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>34</v>
       </c>
@@ -1505,7 +1514,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>35</v>
       </c>
@@ -1525,7 +1534,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>31</v>
       </c>
@@ -1545,7 +1554,7 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>32</v>
       </c>
@@ -1565,29 +1574,29 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="17">
+        <v>20261013</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32">
-        <v>20230127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>14</v>
@@ -1605,69 +1614,69 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="17">
+        <v>20261013</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35">
+        <v>20230127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B36" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C36" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D36" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>20240311</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35">
-        <v>20230127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F36">
-        <v>20230127</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>15</v>
@@ -1685,9 +1694,9 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>15</v>
@@ -1705,55 +1714,55 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="14" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39">
+        <v>20230127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40">
+        <v>20230127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C41" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39">
-        <v>20230127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40">
-        <v>20230127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>41</v>
@@ -1765,15 +1774,15 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>41</v>
@@ -1785,15 +1794,15 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>20</v>
+      <c r="B43" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>41</v>
@@ -1805,55 +1814,55 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" s="5" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>48</v>
+      <c r="E44" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F44">
         <v>20230127</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="5" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>48</v>
+      <c r="E45" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F45">
         <v>20230127</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>23</v>
+      <c r="B46" s="16" t="s">
+        <v>21</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>41</v>
@@ -1865,92 +1874,92 @@
         <v>20230127</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="17" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47">
+        <v>20230127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48">
+        <v>20230127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B49" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C49" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D49" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E49" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F49" s="17">
         <v>20250130</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B50" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C50" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D50" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E50" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F50" s="17">
         <v>20250130</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B49" s="18" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F49" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F50" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>66</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>26</v>
@@ -1965,52 +1974,52 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B52" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F53" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="18" t="s">
         <v>67</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F53" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>69</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>28</v>
@@ -2025,12 +2034,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>28</v>
@@ -2039,18 +2048,18 @@
         <v>29</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F55" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>28</v>
@@ -2059,18 +2068,18 @@
         <v>29</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F56" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>28</v>
@@ -2085,12 +2094,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>28</v>
@@ -2099,18 +2108,18 @@
         <v>29</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F58" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>28</v>
@@ -2119,18 +2128,18 @@
         <v>29</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F59" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>28</v>
@@ -2145,12 +2154,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>28</v>
@@ -2159,18 +2168,18 @@
         <v>29</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>28</v>
@@ -2179,18 +2188,18 @@
         <v>29</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>28</v>
@@ -2205,12 +2214,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>28</v>
@@ -2218,19 +2227,19 @@
       <c r="D64" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E64" s="19" t="s">
-        <v>113</v>
+      <c r="E64" s="18" t="s">
+        <v>112</v>
       </c>
       <c r="F64" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>28</v>
@@ -2238,19 +2247,19 @@
       <c r="D65" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E65" s="19" t="s">
-        <v>113</v>
+      <c r="E65" s="18" t="s">
+        <v>112</v>
       </c>
       <c r="F65" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>28</v>
@@ -2265,52 +2274,52 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B67" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F67" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F68" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="18" t="s">
         <v>82</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F67" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F68" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>84</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>36</v>
@@ -2325,12 +2334,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>36</v>
@@ -2339,18 +2348,18 @@
         <v>37</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F70" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>36</v>
@@ -2359,18 +2368,18 @@
         <v>37</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F71" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>36</v>
@@ -2385,12 +2394,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>36</v>
@@ -2399,18 +2408,18 @@
         <v>37</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>36</v>
@@ -2419,18 +2428,18 @@
         <v>37</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F74" s="17">
         <v>20250110</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>36</v>
@@ -2445,52 +2454,52 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B76" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F76" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F77" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" s="18" t="s">
         <v>91</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F76" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B77" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C77" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D77" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F77" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B78" s="18" t="s">
-        <v>93</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>38</v>
@@ -2505,52 +2514,52 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B79" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F79" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F80" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="C79" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="F79" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B80" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D80" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="F80" s="17">
-        <v>20250110</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B81" s="18" t="s">
-        <v>96</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>45</v>
@@ -2565,15 +2574,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B82" s="19" t="s">
-        <v>97</v>
+      <c r="B82" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D82" s="17" t="s">
         <v>41</v>
@@ -2585,15 +2594,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B83" s="19" t="s">
-        <v>98</v>
+      <c r="B83" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D83" s="17" t="s">
         <v>41</v>
@@ -2605,12 +2614,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>40</v>
@@ -2625,15 +2634,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D85" s="17" t="s">
         <v>41</v>
@@ -2645,15 +2654,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D86" s="17" t="s">
         <v>41</v>
@@ -2665,12 +2674,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>42</v>
@@ -2685,15 +2694,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D88" s="17" t="s">
         <v>41</v>
@@ -2705,15 +2714,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D89" s="17" t="s">
         <v>41</v>
@@ -2725,12 +2734,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>43</v>
@@ -2745,15 +2754,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D91" s="17" t="s">
         <v>41</v>
@@ -2765,15 +2774,15 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D92" s="17" t="s">
         <v>41</v>
@@ -2785,12 +2794,12 @@
         <v>20250110</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>44</v>
@@ -2805,8 +2814,47 @@
         <v>20250110</v>
       </c>
     </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F94" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F95" s="17">
+        <v>20250110</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F46" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2815,20 +2863,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D4B456-9CED-46F7-80B2-919776CEB6BE}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
         <v>121</v>
       </c>
       <c r="B1" s="20"/>
     </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>114</v>
       </c>
@@ -2836,7 +2884,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>116</v>
       </c>
@@ -2844,7 +2892,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>118</v>
       </c>
@@ -2852,7 +2900,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>120</v>
